--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487625_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487625_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.1562</v>
+        <v>6.5844</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1074</v>
+        <v>3.4077</v>
       </c>
       <c r="F2" t="n">
-        <v>4.0488</v>
+        <v>3.1766</v>
       </c>
       <c r="G2" t="n">
         <v>4.8799</v>
@@ -610,13 +610,13 @@
         <v>1.1642</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6954</v>
+        <v>1.1236</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.12</v>
+        <v>0.1803</v>
       </c>
       <c r="U2" t="n">
-        <v>1.8154</v>
+        <v>0.9433</v>
       </c>
       <c r="V2" t="n">
         <v>2.3272</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4636</v>
+        <v>2.4547</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4899</v>
+        <v>2.9904</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.0263</v>
+        <v>-0.5357</v>
       </c>
       <c r="G3" t="n">
         <v>4.7288</v>
@@ -688,13 +688,13 @@
         <v>1.1642</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.6133</v>
+        <v>-0.6222</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9085</v>
+        <v>-0.408</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7048</v>
+        <v>-0.2142</v>
       </c>
       <c r="V3" t="n">
         <v>-0.8758</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.4333</v>
+        <v>-0.0423</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1029</v>
+        <v>0.0973</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3304</v>
+        <v>-0.1396</v>
       </c>
       <c r="G4" t="n">
         <v>2.1077</v>
@@ -766,13 +766,13 @@
         <v>0.5821</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1828</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5451</v>
+        <v>-0.3449</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6377</v>
+        <v>-0.4469</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5483</v>
+        <v>-0.4398</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8376</v>
+        <v>0.5373</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.3859</v>
+        <v>-0.977</v>
       </c>
       <c r="G5" t="n">
         <v>4.8333</v>
@@ -844,13 +844,13 @@
         <v>0.9702</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.5644</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1839</v>
+        <v>-0.1164</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8568</v>
+        <v>-0.448</v>
       </c>
       <c r="V5" t="n">
         <v>-0.828</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.215</v>
+        <v>-2.2051</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.5792</v>
+        <v>-4.0787</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3642</v>
+        <v>1.8736</v>
       </c>
       <c r="G6" t="n">
         <v>2.7695</v>
@@ -922,13 +922,13 @@
         <v>1.3582</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3057</v>
+        <v>-0.2958</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.2719</v>
+        <v>-0.7714</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.4756</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2161</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.7877</v>
+        <v>-2.8967</v>
       </c>
       <c r="E7" t="n">
         <v>-3.4269</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6392</v>
+        <v>0.5302</v>
       </c>
       <c r="G7" t="n">
         <v>-1.1433</v>
@@ -1000,13 +1000,13 @@
         <v>0.9702</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6541</v>
+        <v>0.5451</v>
       </c>
       <c r="T7" t="n">
         <v>-0.12</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7741</v>
+        <v>0.6651</v>
       </c>
       <c r="V7" t="n">
         <v>0.6119</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.0086</v>
+        <v>-3.5736</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.8489</v>
+        <v>-3.8499</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1597</v>
+        <v>0.2764</v>
       </c>
       <c r="G8" t="n">
         <v>-0.8343</v>
@@ -1078,13 +1078,13 @@
         <v>1.1642</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4078</v>
+        <v>0.8429</v>
       </c>
       <c r="T8" t="n">
-        <v>1.5175</v>
+        <v>0.5165</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1097</v>
+        <v>0.3264</v>
       </c>
       <c r="V8" t="n">
         <v>-1.8358</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.6337</v>
+        <v>-6.8884</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.3641</v>
+        <v>-4.5643</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.2697</v>
+        <v>-2.3242</v>
       </c>
       <c r="G9" t="n">
         <v>-2.298</v>
@@ -1156,13 +1156,13 @@
         <v>0.3881</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6554</v>
+        <v>-0.9101</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0595</v>
+        <v>-0.2597</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.596</v>
+        <v>-0.6505</v>
       </c>
       <c r="V9" t="n">
         <v>-1.1579</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.0068</v>
+        <v>-7.006800000000002</v>
       </c>
       <c r="E10" t="n">
-        <v>-8.887099999999998</v>
+        <v>-8.887100000000002</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8802</v>
+        <v>1.880300000000001</v>
       </c>
       <c r="G10" t="n">
         <v>15.0436</v>
@@ -1234,13 +1234,13 @@
         <v>7.7614</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6728000000000001</v>
+        <v>-0.6726999999999999</v>
       </c>
       <c r="T10" t="n">
         <v>-1.3236</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6506999999999998</v>
+        <v>0.6508000000000002</v>
       </c>
       <c r="V10" t="n">
         <v>-1.9745</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>7.4642</v>
+        <v>7.6372</v>
       </c>
       <c r="E11" t="n">
-        <v>6.1642</v>
+        <v>6.3644</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3001</v>
+        <v>1.2728</v>
       </c>
       <c r="G11" t="n">
         <v>2.0398</v>
@@ -1312,13 +1312,13 @@
         <v>2.7164</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1516</v>
+        <v>0.0213</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0617</v>
+        <v>0.2619</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2133</v>
+        <v>-0.2406</v>
       </c>
       <c r="V11" t="n">
         <v>4.7999</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.1571</v>
+        <v>4.0932</v>
       </c>
       <c r="E12" t="n">
-        <v>3.7412</v>
+        <v>3.541</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4159</v>
+        <v>0.5521</v>
       </c>
       <c r="G12" t="n">
         <v>0.99</v>
@@ -1390,13 +1390,13 @@
         <v>3.8806</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0538</v>
+        <v>-0.1178</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4867</v>
+        <v>0.2865</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5406</v>
+        <v>-0.4043</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6597</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.2781</v>
+        <v>2.624</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0192</v>
+        <v>0.4196</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2589</v>
+        <v>2.2044</v>
       </c>
       <c r="G13" t="n">
         <v>-2.0116</v>
@@ -1468,13 +1468,13 @@
         <v>3.8806</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.485</v>
+        <v>-0.1391</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4229</v>
+        <v>-0.0225</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0621</v>
+        <v>-0.1166</v>
       </c>
       <c r="V13" t="n">
         <v>0.894</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2179</v>
+        <v>1.6173</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1364</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="F14" t="n">
         <v>1.0816</v>
@@ -1546,10 +1546,10 @@
         <v>2.9105</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1406</v>
+        <v>0.54</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3358</v>
+        <v>0.7352</v>
       </c>
       <c r="U14" t="n">
         <v>-0.1951</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.967</v>
+        <v>1.2941</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0227</v>
+        <v>-0.3777</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9444</v>
+        <v>1.6718</v>
       </c>
       <c r="G15" t="n">
         <v>-2.2766</v>
@@ -1624,13 +1624,13 @@
         <v>4.2687</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5287</v>
+        <v>0.8557</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7301</v>
+        <v>0.3297</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7986</v>
+        <v>0.526</v>
       </c>
       <c r="V15" t="n">
         <v>-1.5537</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. LASUNCION MARIBLANCA</t>
+          <t>E. PASCUAL COZAR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1274</v>
+        <v>0.2668</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.6998</v>
+        <v>-1.1028</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8272</v>
+        <v>1.3696</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8408</v>
+        <v>-1.6538</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7242</v>
+        <v>-1.0331</v>
       </c>
       <c r="I16" t="n">
-        <v>1.565</v>
+        <v>-0.6206</v>
       </c>
       <c r="J16" t="n">
-        <v>2.4443</v>
+        <v>0.2282</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0618</v>
+        <v>0.1648</v>
       </c>
       <c r="L16" t="n">
-        <v>2.3825</v>
+        <v>0.0634</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.6035</v>
+        <v>-1.882</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.786</v>
+        <v>-1.1979</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8175</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.7164</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9403</v>
+        <v>2.7164</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0536</v>
+        <v>-0.466</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.544</v>
+        <v>-0.6713</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4904</v>
+        <v>0.2053</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6597</v>
+        <v>-0.3299</v>
       </c>
       <c r="W16" t="n">
         <v>-0.6597</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.3299</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. PASCUAL COZAR</t>
+          <t>N. LASUNCION MARIBLANCA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3338</v>
+        <v>0.1547</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.7034</v>
+        <v>-0.6998</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3696</v>
+        <v>0.8544</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.6538</v>
+        <v>0.8408</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0331</v>
+        <v>-0.7242</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6206</v>
+        <v>1.565</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2282</v>
+        <v>2.4443</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1648</v>
+        <v>0.0618</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0634</v>
+        <v>2.3825</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.882</v>
+        <v>-1.6035</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1979</v>
+        <v>-0.786</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.8175</v>
       </c>
       <c r="P17" t="n">
-        <v>2.7164</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7164</v>
+        <v>1.9403</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0666</v>
+        <v>-0.0264</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.2719</v>
+        <v>-0.544</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2053</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3299</v>
+        <v>-0.6597</v>
       </c>
       <c r="W17" t="n">
         <v>-0.6597</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9225</v>
+        <v>-0.8224</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.6568</v>
+        <v>-1.5567</v>
       </c>
       <c r="F18" t="n">
         <v>0.7344000000000001</v>
@@ -1858,10 +1858,10 @@
         <v>0.5821</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1211</v>
+        <v>-0.021</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.424</v>
+        <v>-0.3239</v>
       </c>
       <c r="U18" t="n">
         <v>0.3028</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1998</v>
+        <v>-1.7999</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.0747</v>
+        <v>-2.9746</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8749</v>
+        <v>1.1747</v>
       </c>
       <c r="G19" t="n">
         <v>-3.5039</v>
@@ -1936,13 +1936,13 @@
         <v>1.5523</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2959</v>
+        <v>0.104</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3623</v>
+        <v>-0.2622</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0664</v>
+        <v>0.3662</v>
       </c>
       <c r="V19" t="n">
         <v>0.0478</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.917</v>
+        <v>-3.6082</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.3499</v>
+        <v>-4.8504</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4329</v>
+        <v>1.2421</v>
       </c>
       <c r="G20" t="n">
         <v>-3.9181</v>
@@ -2014,13 +2014,13 @@
         <v>1.7463</v>
       </c>
       <c r="S20" t="n">
-        <v>1.1951</v>
+        <v>0.5039</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2445</v>
+        <v>-0.256</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9507</v>
+        <v>0.7599</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.8319</v>
+        <v>-4.4498</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4794</v>
+        <v>-1.1791</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.3525</v>
+        <v>-3.2707</v>
       </c>
       <c r="G21" t="n">
         <v>-1.7501</v>
@@ -2092,13 +2092,13 @@
         <v>0.9702</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9639</v>
+        <v>-0.5818</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4845</v>
+        <v>-0.1842</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4794</v>
+        <v>-0.3976</v>
       </c>
       <c r="V21" t="n">
         <v>-2.1179</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>7.006700000000001</v>
+        <v>7.006999999999998</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8803</v>
+        <v>-1.880299999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>8.8874</v>
+        <v>8.8872</v>
       </c>
       <c r="G22" t="n">
         <v>-15.0436</v>
@@ -2170,16 +2170,16 @@
         <v>27.1644</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.6728</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6508</v>
+        <v>-0.6508000000000004</v>
       </c>
       <c r="U22" t="n">
-        <v>1.3237</v>
+        <v>1.3236</v>
       </c>
       <c r="V22" t="n">
-        <v>1.9745</v>
+        <v>1.974499999999999</v>
       </c>
       <c r="W22" t="n">
         <v>5.4551</v>
